--- a/files/AFL_goalscorers.xlsx
+++ b/files/AFL_goalscorers.xlsx
@@ -35,18 +35,18 @@
     <t xml:space="preserve">3+ Fair Odds</t>
   </si>
   <si>
-    <t xml:space="preserve">fremantle v geelong cats</t>
+    <t xml:space="preserve">sydney swans v fremantle</t>
   </si>
   <si>
     <t xml:space="preserve">fremantle</t>
   </si>
   <si>
+    <t xml:space="preserve">Jye Amiss</t>
+  </si>
+  <si>
     <t xml:space="preserve">Josh Treacy</t>
   </si>
   <si>
-    <t xml:space="preserve">Jye Amiss</t>
-  </si>
-  <si>
     <t xml:space="preserve">Patrick Voss</t>
   </si>
   <si>
@@ -59,12 +59,12 @@
     <t xml:space="preserve">Luke Jackson</t>
   </si>
   <si>
+    <t xml:space="preserve">Shai Bolton</t>
+  </si>
+  <si>
     <t xml:space="preserve">Murphy Reid</t>
   </si>
   <si>
-    <t xml:space="preserve">Shai Bolton</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sam Switkowski</t>
   </si>
   <si>
@@ -95,121 +95,64 @@
     <t xml:space="preserve">Jordan Clark</t>
   </si>
   <si>
-    <t xml:space="preserve">geelong cats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shannon Neale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shaun Mannagh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jay Polkinghorne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Dangerfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Dempsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oliver Wiltshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brad Close</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gryan Miers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bailey Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Blicavs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Worpel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Atkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oisin Mullin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jhye Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lawson Humphries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brisbane lions v adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adelaide crows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylor Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Thilthorpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Rachele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Keays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izak Rankine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finnbar Maley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zac Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Neal-Bullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Dawson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Soligo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toby Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lachlan McAndrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Cumming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Peatling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Curtin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Berry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Nankervis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayne Milera</t>
+    <t xml:space="preserve">sydney swans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charlie Curnow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan McDonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Papley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Heeney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Billy Cootee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hayden McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chad Warner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malcolm Rosas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braeden Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Rowbottom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errol Gulden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Jordon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Serong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodie Grundy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Blakey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley Bice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn v brisbane lions</t>
   </si>
   <si>
     <t xml:space="preserve">brisbane lions</t>
@@ -236,12 +179,12 @@
     <t xml:space="preserve">Conor McKenna</t>
   </si>
   <si>
+    <t xml:space="preserve">Hugh McCluggage</t>
+  </si>
+  <si>
     <t xml:space="preserve">Will Ashcroft</t>
   </si>
   <si>
-    <t xml:space="preserve">Hugh McCluggage</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sam Draper</t>
   </si>
   <si>
@@ -267,6 +210,63 @@
   </si>
   <si>
     <t xml:space="preserve">Jaspa Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hawthorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Gunston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabior Chol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Lewis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Ginnivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connor Macdonald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliver Greeves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jai Newcombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harry Morrison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lloyd Meek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Hardwick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimo D'Ambrosio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Mackenzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Ward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Weddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jarman Impey</t>
   </si>
 </sst>
 </file>
@@ -604,9 +604,9 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="5.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="31.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="25.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="14.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="12.71" hidden="0" customWidth="1"/>
@@ -637,7 +637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -649,18 +649,18 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -672,18 +672,18 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -695,18 +695,18 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -718,18 +718,18 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="n">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="G5" t="n">
-        <v>9.24</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -741,18 +741,18 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="F6" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9.74</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -764,18 +764,18 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="F7" t="n">
-        <v>4.94</v>
+        <v>5.18</v>
       </c>
       <c r="G7" t="n">
-        <v>19.21</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -787,18 +787,18 @@
         <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="F8" t="n">
-        <v>5.03</v>
+        <v>5.43</v>
       </c>
       <c r="G8" t="n">
-        <v>19.82</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -810,18 +810,18 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="F9" t="n">
-        <v>5.15</v>
+        <v>5.64</v>
       </c>
       <c r="G9" t="n">
-        <v>20.54</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -833,18 +833,18 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="F10" t="n">
-        <v>5.54</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>23.16</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -856,18 +856,18 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="F11" t="n">
-        <v>17.21</v>
+        <v>18.06</v>
       </c>
       <c r="G11" t="n">
-        <v>138.02</v>
+        <v>148.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -879,18 +879,18 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="F12" t="n">
-        <v>21.33</v>
+        <v>23.79</v>
       </c>
       <c r="G12" t="n">
-        <v>192.3</v>
+        <v>227.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -902,18 +902,18 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="F13" t="n">
-        <v>23.9</v>
+        <v>26.37</v>
       </c>
       <c r="G13" t="n">
-        <v>229.23</v>
+        <v>266.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -925,18 +925,18 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>25.43</v>
+        <v>29.25</v>
       </c>
       <c r="G14" t="n">
-        <v>252.3</v>
+        <v>312.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -948,18 +948,18 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>4.07</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="n">
-        <v>30.34</v>
+        <v>34.03</v>
       </c>
       <c r="G15" t="n">
-        <v>331.04</v>
+        <v>394.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
@@ -971,18 +971,18 @@
         <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>4.08</v>
+        <v>4.35</v>
       </c>
       <c r="F16" t="n">
-        <v>30.48</v>
+        <v>34.89</v>
       </c>
       <c r="G16" t="n">
-        <v>333.34</v>
+        <v>410.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -994,18 +994,18 @@
         <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>5.71</v>
+        <v>5.96</v>
       </c>
       <c r="F17" t="n">
-        <v>61.22</v>
+        <v>66.93</v>
       </c>
       <c r="G17" t="n">
-        <v>969.21</v>
+        <v>1110.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1017,18 +1017,18 @@
         <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>6.62</v>
+        <v>7.04</v>
       </c>
       <c r="F18" t="n">
-        <v>83.1</v>
+        <v>94.21</v>
       </c>
       <c r="G18" t="n">
-        <v>1543.46</v>
+        <v>1867.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1040,18 +1040,18 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>11.03</v>
+        <v>12.1</v>
       </c>
       <c r="F19" t="n">
-        <v>235.75</v>
+        <v>284.67</v>
       </c>
       <c r="G19" t="n">
-        <v>7499.88</v>
+        <v>9973</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1063,18 +1063,18 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>4.52</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1086,18 +1086,18 @@
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="G21" t="n">
-        <v>5.54</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
@@ -1109,18 +1109,18 @@
         <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G22" t="n">
-        <v>7.09</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1132,18 +1132,18 @@
         <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="F23" t="n">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="G23" t="n">
-        <v>7.43</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -1155,18 +1155,18 @@
         <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="G24" t="n">
-        <v>9.42</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -1178,18 +1178,18 @@
         <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="F25" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="G25" t="n">
-        <v>12.8</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
@@ -1204,15 +1204,15 @@
         <v>1.69</v>
       </c>
       <c r="F26" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="G26" t="n">
-        <v>16.15</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -1224,18 +1224,18 @@
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>5.03</v>
+        <v>5.15</v>
       </c>
       <c r="G27" t="n">
-        <v>19.81</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -1247,18 +1247,18 @@
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="F28" t="n">
-        <v>5.97</v>
+        <v>6.17</v>
       </c>
       <c r="G28" t="n">
-        <v>26.1</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
@@ -1270,18 +1270,18 @@
         <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="F29" t="n">
-        <v>15.32</v>
+        <v>6.82</v>
       </c>
       <c r="G29" t="n">
-        <v>115.21</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -1293,18 +1293,18 @@
         <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>3.48</v>
+        <v>2.31</v>
       </c>
       <c r="F30" t="n">
-        <v>21.78</v>
+        <v>9.03</v>
       </c>
       <c r="G30" t="n">
-        <v>198.67</v>
+        <v>50.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -1316,18 +1316,18 @@
         <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>3.77</v>
+        <v>2.92</v>
       </c>
       <c r="F31" t="n">
-        <v>25.77</v>
+        <v>14.96</v>
       </c>
       <c r="G31" t="n">
-        <v>257.43</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -1339,18 +1339,18 @@
         <v>40</v>
       </c>
       <c r="E32" t="n">
-        <v>4.18</v>
+        <v>3.61</v>
       </c>
       <c r="F32" t="n">
-        <v>32.05</v>
+        <v>23.55</v>
       </c>
       <c r="G32" t="n">
-        <v>360.02</v>
+        <v>224.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B33" t="s">
         <v>7</v>
@@ -1362,18 +1362,18 @@
         <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>5.05</v>
+        <v>3.74</v>
       </c>
       <c r="F33" t="n">
-        <v>47.53</v>
+        <v>25.35</v>
       </c>
       <c r="G33" t="n">
-        <v>658.55</v>
+        <v>251.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
@@ -1385,18 +1385,18 @@
         <v>42</v>
       </c>
       <c r="E34" t="n">
-        <v>5.35</v>
+        <v>3.95</v>
       </c>
       <c r="F34" t="n">
-        <v>53.63</v>
+        <v>28.47</v>
       </c>
       <c r="G34" t="n">
-        <v>791.88</v>
+        <v>300.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -1408,18 +1408,18 @@
         <v>43</v>
       </c>
       <c r="E35" t="n">
-        <v>6.5</v>
+        <v>4.58</v>
       </c>
       <c r="F35" t="n">
-        <v>80.07</v>
+        <v>38.82</v>
       </c>
       <c r="G35" t="n">
-        <v>1458.56</v>
+        <v>483.18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -1431,18 +1431,18 @@
         <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>6.84</v>
+        <v>5.37</v>
       </c>
       <c r="F36" t="n">
-        <v>88.85</v>
+        <v>53.91</v>
       </c>
       <c r="G36" t="n">
-        <v>1708.73</v>
+        <v>798.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -1454,18 +1454,18 @@
         <v>45</v>
       </c>
       <c r="E37" t="n">
-        <v>6.88</v>
+        <v>9.6</v>
       </c>
       <c r="F37" t="n">
-        <v>90.03</v>
+        <v>177.74</v>
       </c>
       <c r="G37" t="n">
-        <v>1743.25</v>
+        <v>4891.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B38" t="s">
         <v>46</v>
@@ -1477,18 +1477,18 @@
         <v>48</v>
       </c>
       <c r="E38" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="F38" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="G38" t="n">
-        <v>4.66</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -1500,18 +1500,18 @@
         <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="F39" t="n">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="G39" t="n">
-        <v>5.01</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -1523,18 +1523,18 @@
         <v>50</v>
       </c>
       <c r="E40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="F40" t="n">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="G40" t="n">
-        <v>6.1</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
@@ -1546,18 +1546,18 @@
         <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="G41" t="n">
-        <v>8.46</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -1569,18 +1569,18 @@
         <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="F42" t="n">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="G42" t="n">
-        <v>12.24</v>
+        <v>9.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
@@ -1592,18 +1592,18 @@
         <v>53</v>
       </c>
       <c r="E43" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="F43" t="n">
-        <v>6.14</v>
+        <v>3.38</v>
       </c>
       <c r="G43" t="n">
-        <v>27.29</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
@@ -1615,18 +1615,18 @@
         <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="F44" t="n">
-        <v>6.87</v>
+        <v>3.82</v>
       </c>
       <c r="G44" t="n">
-        <v>32.66</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
@@ -1638,18 +1638,18 @@
         <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="F45" t="n">
-        <v>7.07</v>
+        <v>8.9</v>
       </c>
       <c r="G45" t="n">
-        <v>34.17</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
@@ -1661,18 +1661,18 @@
         <v>56</v>
       </c>
       <c r="E46" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="F46" t="n">
-        <v>8.12</v>
+        <v>9.72</v>
       </c>
       <c r="G46" t="n">
-        <v>42.57</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
@@ -1684,18 +1684,18 @@
         <v>57</v>
       </c>
       <c r="E47" t="n">
-        <v>2.23</v>
+        <v>2.61</v>
       </c>
       <c r="F47" t="n">
-        <v>8.3</v>
+        <v>11.79</v>
       </c>
       <c r="G47" t="n">
-        <v>44.09</v>
+        <v>76.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
@@ -1707,18 +1707,18 @@
         <v>58</v>
       </c>
       <c r="E48" t="n">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="F48" t="n">
-        <v>19.84</v>
+        <v>12.66</v>
       </c>
       <c r="G48" t="n">
-        <v>171.92</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
@@ -1730,18 +1730,18 @@
         <v>59</v>
       </c>
       <c r="E49" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="F49" t="n">
-        <v>22.59</v>
+        <v>24.57</v>
       </c>
       <c r="G49" t="n">
-        <v>210.14</v>
+        <v>239.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
@@ -1753,18 +1753,18 @@
         <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="F50" t="n">
-        <v>23.32</v>
+        <v>25.04</v>
       </c>
       <c r="G50" t="n">
-        <v>220.81</v>
+        <v>246.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
@@ -1776,18 +1776,18 @@
         <v>61</v>
       </c>
       <c r="E51" t="n">
-        <v>3.98</v>
+        <v>3.86</v>
       </c>
       <c r="F51" t="n">
-        <v>28.89</v>
+        <v>27.17</v>
       </c>
       <c r="G51" t="n">
-        <v>306.95</v>
+        <v>279.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
@@ -1799,18 +1799,18 @@
         <v>62</v>
       </c>
       <c r="E52" t="n">
-        <v>4.03</v>
+        <v>4.46</v>
       </c>
       <c r="F52" t="n">
-        <v>29.71</v>
+        <v>36.64</v>
       </c>
       <c r="G52" t="n">
-        <v>320.46</v>
+        <v>442.18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
@@ -1822,18 +1822,18 @@
         <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>5.08</v>
+        <v>4.51</v>
       </c>
       <c r="F53" t="n">
-        <v>48.14</v>
+        <v>37.58</v>
       </c>
       <c r="G53" t="n">
-        <v>671.43</v>
+        <v>459.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
@@ -1845,18 +1845,18 @@
         <v>64</v>
       </c>
       <c r="E54" t="n">
-        <v>8.2</v>
+        <v>5.39</v>
       </c>
       <c r="F54" t="n">
-        <v>128.95</v>
+        <v>54.32</v>
       </c>
       <c r="G54" t="n">
-        <v>3008.1</v>
+        <v>807.62</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
@@ -1868,18 +1868,18 @@
         <v>65</v>
       </c>
       <c r="E55" t="n">
-        <v>10.7</v>
+        <v>6.51</v>
       </c>
       <c r="F55" t="n">
-        <v>221.55</v>
+        <v>80.23</v>
       </c>
       <c r="G55" t="n">
-        <v>6827.53</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
@@ -1891,18 +1891,18 @@
         <v>67</v>
       </c>
       <c r="E56" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="F56" t="n">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="G56" t="n">
-        <v>3.03</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
@@ -1914,18 +1914,18 @@
         <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="F57" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="G57" t="n">
-        <v>4.38</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
@@ -1937,18 +1937,18 @@
         <v>69</v>
       </c>
       <c r="E58" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="F58" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="G58" t="n">
-        <v>4.42</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B59" t="s">
         <v>46</v>
@@ -1960,18 +1960,18 @@
         <v>70</v>
       </c>
       <c r="E59" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F59" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="G59" t="n">
-        <v>7.27</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B60" t="s">
         <v>46</v>
@@ -1983,18 +1983,18 @@
         <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="F60" t="n">
-        <v>3.02</v>
+        <v>4.02</v>
       </c>
       <c r="G60" t="n">
-        <v>8.58</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B61" t="s">
         <v>46</v>
@@ -2006,18 +2006,18 @@
         <v>72</v>
       </c>
       <c r="E61" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="F61" t="n">
-        <v>3.06</v>
+        <v>4.05</v>
       </c>
       <c r="G61" t="n">
-        <v>8.73</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B62" t="s">
         <v>46</v>
@@ -2029,18 +2029,18 @@
         <v>73</v>
       </c>
       <c r="E62" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="F62" t="n">
-        <v>3.6</v>
+        <v>5.31</v>
       </c>
       <c r="G62" t="n">
-        <v>11.48</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B63" t="s">
         <v>46</v>
@@ -2052,18 +2052,18 @@
         <v>74</v>
       </c>
       <c r="E63" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="F63" t="n">
-        <v>8.76</v>
+        <v>5.5</v>
       </c>
       <c r="G63" t="n">
-        <v>47.97</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B64" t="s">
         <v>46</v>
@@ -2075,18 +2075,18 @@
         <v>75</v>
       </c>
       <c r="E64" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="F64" t="n">
-        <v>9.18</v>
+        <v>12.5</v>
       </c>
       <c r="G64" t="n">
-        <v>51.71</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B65" t="s">
         <v>46</v>
@@ -2098,18 +2098,18 @@
         <v>76</v>
       </c>
       <c r="E65" t="n">
-        <v>2.46</v>
+        <v>3.23</v>
       </c>
       <c r="F65" t="n">
-        <v>10.33</v>
+        <v>18.59</v>
       </c>
       <c r="G65" t="n">
-        <v>62.26</v>
+        <v>155.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B66" t="s">
         <v>46</v>
@@ -2121,18 +2121,18 @@
         <v>77</v>
       </c>
       <c r="E66" t="n">
-        <v>2.66</v>
+        <v>3.57</v>
       </c>
       <c r="F66" t="n">
-        <v>12.25</v>
+        <v>22.96</v>
       </c>
       <c r="G66" t="n">
-        <v>81.24</v>
+        <v>215.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B67" t="s">
         <v>46</v>
@@ -2144,18 +2144,18 @@
         <v>78</v>
       </c>
       <c r="E67" t="n">
-        <v>3.46</v>
+        <v>3.92</v>
       </c>
       <c r="F67" t="n">
-        <v>21.55</v>
+        <v>27.95</v>
       </c>
       <c r="G67" t="n">
-        <v>195.44</v>
+        <v>291.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B68" t="s">
         <v>46</v>
@@ -2167,18 +2167,18 @@
         <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>3.54</v>
+        <v>4.01</v>
       </c>
       <c r="F68" t="n">
-        <v>22.53</v>
+        <v>29.41</v>
       </c>
       <c r="G68" t="n">
-        <v>209.3</v>
+        <v>315.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B69" t="s">
         <v>46</v>
@@ -2190,18 +2190,18 @@
         <v>80</v>
       </c>
       <c r="E69" t="n">
-        <v>3.74</v>
+        <v>4.14</v>
       </c>
       <c r="F69" t="n">
-        <v>25.29</v>
+        <v>31.43</v>
       </c>
       <c r="G69" t="n">
-        <v>250.15</v>
+        <v>349.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B70" t="s">
         <v>46</v>
@@ -2213,18 +2213,18 @@
         <v>81</v>
       </c>
       <c r="E70" t="n">
-        <v>4.19</v>
+        <v>4.31</v>
       </c>
       <c r="F70" t="n">
-        <v>32.24</v>
+        <v>34.21</v>
       </c>
       <c r="G70" t="n">
-        <v>363.33</v>
+        <v>398.06</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -2236,18 +2236,18 @@
         <v>82</v>
       </c>
       <c r="E71" t="n">
-        <v>4.29</v>
+        <v>4.44</v>
       </c>
       <c r="F71" t="n">
-        <v>33.74</v>
+        <v>36.34</v>
       </c>
       <c r="G71" t="n">
-        <v>389.69</v>
+        <v>436.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B72" t="s">
         <v>46</v>
@@ -2259,18 +2259,18 @@
         <v>83</v>
       </c>
       <c r="E72" t="n">
-        <v>5.6</v>
+        <v>4.74</v>
       </c>
       <c r="F72" t="n">
-        <v>58.89</v>
+        <v>41.58</v>
       </c>
       <c r="G72" t="n">
-        <v>913.57</v>
+        <v>536.65</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
@@ -2282,13 +2282,13 @@
         <v>84</v>
       </c>
       <c r="E73" t="n">
-        <v>6.14</v>
+        <v>6.21</v>
       </c>
       <c r="F73" t="n">
-        <v>71.27</v>
+        <v>72.96</v>
       </c>
       <c r="G73" t="n">
-        <v>1221.72</v>
+        <v>1266.08</v>
       </c>
     </row>
   </sheetData>
